--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/atacama.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1133261-210-CM25</t>
+          <t>4355-207-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SEIDOR TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.449.580-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7518.42</v>
+        <v>44982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1172445-2366-CM25</t>
+          <t>4192-2857-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.810-9</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>48452.04</v>
+        <v>47113.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3703-676-CM25</t>
+          <t>2923-355-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.030.700-6</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUASCO</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8899.5</v>
+        <v>10033.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4192-33-CM26</t>
+          <t>4357-311-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.030.300-0</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALDERA</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>55827.66</v>
+        <v>3848.46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1151575-9-CM26</t>
+          <t>4193-395-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.195.573-4</t>
+          <t>69.030.300-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3077.82</v>
+        <v>28244.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2923-518-CM26</t>
+          <t>751-1470-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10024.98</v>
+        <v>20706</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4357-214-CM26</t>
+          <t>1133261-210-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>62.000.810-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,7 +935,495 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>7518.42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1172445-2366-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>62.000.810-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION PÚBLICA DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>48452.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3703-676-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.030.700-6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>8899.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4192-33-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CLOUDLATAM SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.981.642-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>55827.66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1151575-9-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>65.195.573-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3077.82</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2923-518-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.030.100-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>10024.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4357-214-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.030.600-k</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>3846.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4193-366-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.030.300-0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALDERA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>53273.68</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>751-300-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>72.232.200-2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>21124.88</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/atacama.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.981.642-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
